--- a/已完成材料/汇总表.xlsx
+++ b/已完成材料/汇总表.xlsx
@@ -1481,7 +1481,9 @@
       <c r="G4" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="H4" s="10"/>
+      <c r="H4" s="10">
+        <v>13795580188</v>
+      </c>
       <c r="I4" s="10" t="s">
         <v>19</v>
       </c>
